--- a/engagement_survey_forms/034_lgbtq_allyship_in_nonprofits_survey--engagement_survey_forms.xlsx
+++ b/engagement_survey_forms/034_lgbtq_allyship_in_nonprofits_survey--engagement_survey_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'prefer_not_to_say'}</t>
+          <t>prefer_not_to_say</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Prefer not to say'}</t>
+          <t>Prefer not to say</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'communication_barriers'}</t>
+          <t>communication_barriers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Communication barriers'}</t>
+          <t>Communication barriers</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'lack_of_training'}</t>
+          <t>lack_of_training</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Lack of training'}</t>
+          <t>Lack of training</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fear_of_saying_the_wrong_thing'}</t>
+          <t>fear_of_saying_the_wrong_thing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fear of saying the wrong thing'}</t>
+          <t>Fear of saying the wrong thing</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'communication_skills'}</t>
+          <t>communication_skills</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Communication skills'}</t>
+          <t>Communication skills</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'understanding_the_lgbtq+_community'}</t>
+          <t>understanding_the_lgbtq+_community</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Understanding the LGBTQ+ community'}</t>
+          <t>Understanding the LGBTQ+ community</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'leadership_and_management'}</t>
+          <t>leadership_and_management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Leadership and management'}</t>
+          <t>Leadership and management</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
